--- a/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,145 +448,277 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>r7QOmnxn</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
-      </c>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fBoFTriU</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D3" t="n">
-        <v>15</v>
-      </c>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QVFTn6ih</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.5</v>
-      </c>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8EBlrr6N</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.7</v>
-      </c>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YeJyopM4</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.05</v>
-      </c>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fB7pqOjH</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WWMKlSMu</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3.3</v>
-      </c>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CnIup4yB</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2.9</v>
-      </c>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4MEXoQ6b</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2.15</v>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4.45</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,17 +708,57 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="C28" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="D28" t="n">
-        <v>4.45</v>
+      <c r="B32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
+++ b/p6_deployment/data/germany/data_preparation/format_data/df_match_odds_form.xlsx
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="C32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
     </row>
   </sheetData>
